--- a/data/nzd0579/nzd0579.xlsx
+++ b/data/nzd0579/nzd0579.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G915"/>
+  <dimension ref="A1:G917"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25141,6 +25141,60 @@
         <v>214.75</v>
       </c>
       <c r="G915" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:12:25+00:00</t>
+        </is>
+      </c>
+      <c r="B916" t="n">
+        <v>257.76</v>
+      </c>
+      <c r="C916" t="n">
+        <v>226.83</v>
+      </c>
+      <c r="D916" t="n">
+        <v>225.74</v>
+      </c>
+      <c r="E916" t="n">
+        <v>216.97</v>
+      </c>
+      <c r="F916" t="n">
+        <v>214.8</v>
+      </c>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:06:36+00:00</t>
+        </is>
+      </c>
+      <c r="B917" t="n">
+        <v>255.99</v>
+      </c>
+      <c r="C917" t="n">
+        <v>227.36</v>
+      </c>
+      <c r="D917" t="n">
+        <v>226.68</v>
+      </c>
+      <c r="E917" t="n">
+        <v>217.44</v>
+      </c>
+      <c r="F917" t="n">
+        <v>214.51</v>
+      </c>
+      <c r="G917" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -25157,7 +25211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B968"/>
+  <dimension ref="A1:B970"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34840,6 +34894,26 @@
       </c>
       <c r="B968" t="n">
         <v>0.98</v>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B969" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B970" t="n">
+        <v>1.12</v>
       </c>
     </row>
   </sheetData>
@@ -35002,28 +35076,28 @@
         <v>0.0419</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2915515085394432</v>
+        <v>-0.2839552984018376</v>
       </c>
       <c r="J2" t="n">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="K2" t="n">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="L2" t="n">
-        <v>0.025654613259945</v>
+        <v>0.02440938877393128</v>
       </c>
       <c r="M2" t="n">
-        <v>10.6737498691717</v>
+        <v>10.68516926901931</v>
       </c>
       <c r="N2" t="n">
-        <v>184.2252414049774</v>
+        <v>184.457059257079</v>
       </c>
       <c r="O2" t="n">
-        <v>13.57295993528963</v>
+        <v>13.58149694463313</v>
       </c>
       <c r="P2" t="n">
-        <v>247.6335224299428</v>
+        <v>247.5550604429799</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35074,28 +35148,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1482192501103053</v>
+        <v>0.1482844798417591</v>
       </c>
       <c r="J3" t="n">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="K3" t="n">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03329896093757079</v>
+        <v>0.03349538829450405</v>
       </c>
       <c r="M3" t="n">
-        <v>4.544588225551299</v>
+        <v>4.535242774009173</v>
       </c>
       <c r="N3" t="n">
-        <v>36.39500758482058</v>
+        <v>36.31574262919288</v>
       </c>
       <c r="O3" t="n">
-        <v>6.03282749503254</v>
+        <v>6.02625444444498</v>
       </c>
       <c r="P3" t="n">
-        <v>222.9616672620648</v>
+        <v>222.9609923082014</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35146,28 +35220,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4656746146240857</v>
+        <v>0.4664025320593889</v>
       </c>
       <c r="J4" t="n">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="K4" t="n">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3881863335322393</v>
+        <v>0.3900909794467338</v>
       </c>
       <c r="M4" t="n">
-        <v>3.208711453835085</v>
+        <v>3.205193200046491</v>
       </c>
       <c r="N4" t="n">
-        <v>19.5036164344898</v>
+        <v>19.46729308883035</v>
       </c>
       <c r="O4" t="n">
-        <v>4.416289894752133</v>
+        <v>4.412175550545371</v>
       </c>
       <c r="P4" t="n">
-        <v>212.0487677960474</v>
+        <v>212.0412466958154</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35218,28 +35292,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5734816359760632</v>
+        <v>0.5726957039547682</v>
       </c>
       <c r="J5" t="n">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="K5" t="n">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="L5" t="n">
-        <v>0.508178970489874</v>
+        <v>0.5087008604912318</v>
       </c>
       <c r="M5" t="n">
-        <v>3.448811353352429</v>
+        <v>3.445169125076876</v>
       </c>
       <c r="N5" t="n">
-        <v>18.16354122146324</v>
+        <v>18.13075967410202</v>
       </c>
       <c r="O5" t="n">
-        <v>4.261870624674479</v>
+        <v>4.258022977169336</v>
       </c>
       <c r="P5" t="n">
-        <v>203.5460793990883</v>
+        <v>203.5541968047087</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35290,28 +35364,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5918882067265999</v>
+        <v>0.5912261082623983</v>
       </c>
       <c r="J6" t="n">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="K6" t="n">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="L6" t="n">
-        <v>0.585091892127074</v>
+        <v>0.585729850998493</v>
       </c>
       <c r="M6" t="n">
-        <v>2.927573956208424</v>
+        <v>2.924553939726081</v>
       </c>
       <c r="N6" t="n">
-        <v>14.17680294232691</v>
+        <v>14.15070607333215</v>
       </c>
       <c r="O6" t="n">
-        <v>3.765209548262475</v>
+        <v>3.761742425171101</v>
       </c>
       <c r="P6" t="n">
-        <v>200.224601556655</v>
+        <v>200.2314414647701</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35349,7 +35423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G915"/>
+  <dimension ref="A1:G917"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69207,6 +69281,80 @@
         </is>
       </c>
     </row>
+    <row r="916">
+      <c r="A916" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:12:25+00:00</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>-40.94750488049012,173.0501336487484</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>-40.946848093571454,173.0496847631573</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>-40.94614840220512,173.04970657268328</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>-40.945439269221886,173.04972742604335</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>-40.94478278799517,173.04996874695814</t>
+        </is>
+      </c>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:06:36+00:00</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>-40.94750672285489,173.05011276029236</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>-40.946848093080696,173.04969106000684</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>-40.94614912476262,173.0497176998309</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>-40.94543994594747,173.04973293813595</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>-40.944781772859095,173.04996557237388</t>
+        </is>
+      </c>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0579/nzd0579.xlsx
+++ b/data/nzd0579/nzd0579.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G917"/>
+  <dimension ref="A1:G919"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25195,6 +25195,60 @@
         <v>214.51</v>
       </c>
       <c r="G917" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B918" t="n">
+        <v>255.45</v>
+      </c>
+      <c r="C918" t="n">
+        <v>227.15</v>
+      </c>
+      <c r="D918" t="n">
+        <v>226.39</v>
+      </c>
+      <c r="E918" t="n">
+        <v>217.83</v>
+      </c>
+      <c r="F918" t="n">
+        <v>214.3</v>
+      </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:12:48+00:00</t>
+        </is>
+      </c>
+      <c r="B919" t="n">
+        <v>251.17</v>
+      </c>
+      <c r="C919" t="n">
+        <v>227.36</v>
+      </c>
+      <c r="D919" t="n">
+        <v>226.78</v>
+      </c>
+      <c r="E919" t="n">
+        <v>217.9</v>
+      </c>
+      <c r="F919" t="n">
+        <v>213.65</v>
+      </c>
+      <c r="G919" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -25211,7 +25265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B970"/>
+  <dimension ref="A1:B972"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34914,6 +34968,26 @@
       </c>
       <c r="B970" t="n">
         <v>1.12</v>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B971" t="n">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B972" t="n">
+        <v>-0.84</v>
       </c>
     </row>
   </sheetData>
@@ -35076,28 +35150,28 @@
         <v>0.0419</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2839552984018376</v>
+        <v>-0.2780031216169657</v>
       </c>
       <c r="J2" t="n">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="K2" t="n">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02440938877393128</v>
+        <v>0.02349042135429846</v>
       </c>
       <c r="M2" t="n">
-        <v>10.68516926901931</v>
+        <v>10.68895723107763</v>
       </c>
       <c r="N2" t="n">
-        <v>184.457059257079</v>
+        <v>184.454177186026</v>
       </c>
       <c r="O2" t="n">
-        <v>13.58149694463313</v>
+        <v>13.58139084136916</v>
       </c>
       <c r="P2" t="n">
-        <v>247.5550604429799</v>
+        <v>247.4934251837091</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35148,28 +35222,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1482844798417591</v>
+        <v>0.1484161432083543</v>
       </c>
       <c r="J3" t="n">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="K3" t="n">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03349538829450405</v>
+        <v>0.03372231740317833</v>
       </c>
       <c r="M3" t="n">
-        <v>4.535242774009173</v>
+        <v>4.525998413705603</v>
       </c>
       <c r="N3" t="n">
-        <v>36.31574262919288</v>
+        <v>36.23683593367884</v>
       </c>
       <c r="O3" t="n">
-        <v>6.02625444444498</v>
+        <v>6.019703973924203</v>
       </c>
       <c r="P3" t="n">
-        <v>222.9609923082014</v>
+        <v>222.9596283157695</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35220,28 +35294,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4664025320593889</v>
+        <v>0.4672764216736841</v>
       </c>
       <c r="J4" t="n">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="K4" t="n">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3900909794467338</v>
+        <v>0.3921214907631271</v>
       </c>
       <c r="M4" t="n">
-        <v>3.205193200046491</v>
+        <v>3.202399789375165</v>
       </c>
       <c r="N4" t="n">
-        <v>19.46729308883035</v>
+        <v>19.43333461376014</v>
       </c>
       <c r="O4" t="n">
-        <v>4.412175550545371</v>
+        <v>4.408325602058013</v>
       </c>
       <c r="P4" t="n">
-        <v>212.0412466958154</v>
+        <v>212.0321954599524</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35292,28 +35366,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5726957039547682</v>
+        <v>0.5721947359527783</v>
       </c>
       <c r="J5" t="n">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="K5" t="n">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5087008604912318</v>
+        <v>0.5095293779180095</v>
       </c>
       <c r="M5" t="n">
-        <v>3.445169125076876</v>
+        <v>3.440123258198971</v>
       </c>
       <c r="N5" t="n">
-        <v>18.13075967410202</v>
+        <v>18.0940145579017</v>
       </c>
       <c r="O5" t="n">
-        <v>4.258022977169336</v>
+        <v>4.253705979249354</v>
       </c>
       <c r="P5" t="n">
-        <v>203.5541968047087</v>
+        <v>203.5593850150053</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35364,28 +35438,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5912261082623983</v>
+        <v>0.5902493533475538</v>
       </c>
       <c r="J6" t="n">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="K6" t="n">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="L6" t="n">
-        <v>0.585729850998493</v>
+        <v>0.5860094286880444</v>
       </c>
       <c r="M6" t="n">
-        <v>2.924553939726081</v>
+        <v>2.923179688440824</v>
       </c>
       <c r="N6" t="n">
-        <v>14.15070607333215</v>
+        <v>14.13059129590872</v>
       </c>
       <c r="O6" t="n">
-        <v>3.761742425171101</v>
+        <v>3.75906787593796</v>
       </c>
       <c r="P6" t="n">
-        <v>200.2314414647701</v>
+        <v>200.2415586515432</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35423,7 +35497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G917"/>
+  <dimension ref="A1:G919"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69355,6 +69429,80 @@
         </is>
       </c>
     </row>
+    <row r="918">
+      <c r="A918" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>-40.94750728493152,173.05010638754283</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>-40.94684809327518,173.0496885650287</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>-40.94614890184606,173.04971426698748</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>-40.945440507485536,173.04973751200012</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>-40.94478103776051,173.04996327353706</t>
+        </is>
+      </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:12:48+00:00</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>-40.947511739896854,173.05005587759828</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>-40.946848093080696,173.04969106000684</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>-40.94614920163037,173.04971888357005</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>-40.94544060827439,173.0497383329501</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>-40.94477876245503,173.04995615809008</t>
+        </is>
+      </c>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0579/nzd0579.xlsx
+++ b/data/nzd0579/nzd0579.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G919"/>
+  <dimension ref="A1:G923"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25249,6 +25249,114 @@
         <v>213.65</v>
       </c>
       <c r="G919" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-21 22:06:35+00:00</t>
+        </is>
+      </c>
+      <c r="B920" t="n">
+        <v>250.21</v>
+      </c>
+      <c r="C920" t="n">
+        <v>227.35</v>
+      </c>
+      <c r="D920" t="n">
+        <v>226.62</v>
+      </c>
+      <c r="E920" t="n">
+        <v>218.08</v>
+      </c>
+      <c r="F920" t="n">
+        <v>213.85</v>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B921" t="n">
+        <v>250.91</v>
+      </c>
+      <c r="C921" t="n">
+        <v>227.71</v>
+      </c>
+      <c r="D921" t="n">
+        <v>226.67</v>
+      </c>
+      <c r="E921" t="n">
+        <v>218.09</v>
+      </c>
+      <c r="F921" t="n">
+        <v>214.12</v>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:12:52+00:00</t>
+        </is>
+      </c>
+      <c r="B922" t="n">
+        <v>251.1</v>
+      </c>
+      <c r="C922" t="n">
+        <v>227.81</v>
+      </c>
+      <c r="D922" t="n">
+        <v>227.19</v>
+      </c>
+      <c r="E922" t="n">
+        <v>218.39</v>
+      </c>
+      <c r="F922" t="n">
+        <v>213.89</v>
+      </c>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:12+00:00</t>
+        </is>
+      </c>
+      <c r="B923" t="n">
+        <v>250.92</v>
+      </c>
+      <c r="C923" t="n">
+        <v>227.99</v>
+      </c>
+      <c r="D923" t="n">
+        <v>227.09</v>
+      </c>
+      <c r="E923" t="n">
+        <v>218.55</v>
+      </c>
+      <c r="F923" t="n">
+        <v>214.15</v>
+      </c>
+      <c r="G923" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -25265,7 +25373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B972"/>
+  <dimension ref="A1:B976"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34988,6 +35096,46 @@
       </c>
       <c r="B972" t="n">
         <v>-0.84</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>2026-08-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B973" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B974" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B975" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B976" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -35150,28 +35298,28 @@
         <v>0.0419</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2780031216169657</v>
+        <v>-0.268499310067951</v>
       </c>
       <c r="J2" t="n">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="K2" t="n">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02349042135429846</v>
+        <v>0.02211185343923305</v>
       </c>
       <c r="M2" t="n">
-        <v>10.68895723107763</v>
+        <v>10.68593330262109</v>
       </c>
       <c r="N2" t="n">
-        <v>184.454177186026</v>
+        <v>184.1536502293726</v>
       </c>
       <c r="O2" t="n">
-        <v>13.58139084136916</v>
+        <v>13.5703224069796</v>
       </c>
       <c r="P2" t="n">
-        <v>247.4934251837091</v>
+        <v>247.3947512528327</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35222,28 +35370,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1484161432083543</v>
+        <v>0.1490720930427739</v>
       </c>
       <c r="J3" t="n">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="K3" t="n">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03372231740317833</v>
+        <v>0.03435170021955991</v>
       </c>
       <c r="M3" t="n">
-        <v>4.525998413705603</v>
+        <v>4.509518577060512</v>
       </c>
       <c r="N3" t="n">
-        <v>36.23683593367884</v>
+        <v>36.08223164201375</v>
       </c>
       <c r="O3" t="n">
-        <v>6.019703973924203</v>
+        <v>6.006848728078121</v>
       </c>
       <c r="P3" t="n">
-        <v>222.9596283157695</v>
+        <v>222.9528159060991</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35294,28 +35442,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4672764216736841</v>
+        <v>0.4692386796274938</v>
       </c>
       <c r="J4" t="n">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="K4" t="n">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3921214907631271</v>
+        <v>0.3963401375839565</v>
       </c>
       <c r="M4" t="n">
-        <v>3.202399789375165</v>
+        <v>3.197820297692591</v>
       </c>
       <c r="N4" t="n">
-        <v>19.43333461376014</v>
+        <v>19.37054328608696</v>
       </c>
       <c r="O4" t="n">
-        <v>4.408325602058013</v>
+        <v>4.401197937617321</v>
       </c>
       <c r="P4" t="n">
-        <v>212.0321954599524</v>
+        <v>212.0118203927674</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35366,28 +35514,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5721947359527783</v>
+        <v>0.5715413784345901</v>
       </c>
       <c r="J5" t="n">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="K5" t="n">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5095293779180095</v>
+        <v>0.5115213026467629</v>
       </c>
       <c r="M5" t="n">
-        <v>3.440123258198971</v>
+        <v>3.428379144000316</v>
       </c>
       <c r="N5" t="n">
-        <v>18.0940145579017</v>
+        <v>18.01802596889087</v>
       </c>
       <c r="O5" t="n">
-        <v>4.253705979249354</v>
+        <v>4.24476453633071</v>
       </c>
       <c r="P5" t="n">
-        <v>203.5593850150053</v>
+        <v>203.5661665279826</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35438,28 +35586,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5902493533475538</v>
+        <v>0.5883217360798664</v>
       </c>
       <c r="J6" t="n">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="K6" t="n">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5860094286880444</v>
+        <v>0.5865890113901664</v>
       </c>
       <c r="M6" t="n">
-        <v>2.923179688440824</v>
+        <v>2.920366180685711</v>
       </c>
       <c r="N6" t="n">
-        <v>14.13059129590872</v>
+        <v>14.08989738068381</v>
       </c>
       <c r="O6" t="n">
-        <v>3.75906787593796</v>
+        <v>3.753651206583239</v>
       </c>
       <c r="P6" t="n">
-        <v>200.2415586515432</v>
+        <v>200.2615713579696</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35497,7 +35645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G919"/>
+  <dimension ref="A1:G923"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69503,6 +69651,154 @@
         </is>
       </c>
     </row>
+    <row r="920">
+      <c r="A920" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-21 22:06:35+00:00</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>-40.94751273913837,173.050044548264</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>-40.94684809308995,173.04969094119835</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>-40.94614907864195,173.04971698958744</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>-40.945440867445726,173.04974044396437</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>-40.944779462549064,173.04995834745833</t>
+        </is>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:12:49+00:00</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>-40.947512010524854,173.05005280923694</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>-40.94684809275641,173.0496952183037</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>-40.94614911707584,173.049717581457</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>-40.94544088184414,173.04974056124297</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>-40.944780407675935,173.04996130310553</t>
+        </is>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:12:52+00:00</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>-40.94751181275825,173.050055051501</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>-40.94684809266374,173.04969640638853</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>-40.94614951678804,173.04972373690046</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>-40.945441313796266,173.0497440796001</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>-40.94477960256787,173.049958785332</t>
+        </is>
+      </c>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:12+00:00</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>-40.9475120001161,173.05005292725085</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>-40.94684809249688,173.0496985449412</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>-40.94614943992033,173.04972255316136</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>-40.945441544170706,173.04974595605725</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>-40.944780512690045,173.0499616315108</t>
+        </is>
+      </c>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
